--- a/src/assets/newportfoliodata.xlsx
+++ b/src/assets/newportfoliodata.xlsx
@@ -12,7 +12,6 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="125725"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -404,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.85546875" customWidth="1"/>
@@ -1107,37 +1106,15 @@
       </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="6">
-        <v>45929</v>
-      </c>
-      <c r="B22" s="2">
-        <v>3500</v>
-      </c>
-      <c r="C22" s="3">
-        <f t="shared" ref="C22" si="8">B22/100000*100</f>
-        <v>3.5000000000000004</v>
-      </c>
-      <c r="D22" s="2">
-        <v>3000</v>
-      </c>
-      <c r="E22" s="3">
-        <f t="shared" ref="E22" si="9">D22/100000*100</f>
-        <v>3</v>
-      </c>
-      <c r="F22" s="2">
-        <v>4000</v>
-      </c>
-      <c r="G22" s="3">
-        <f t="shared" ref="G22" si="10">F22/100000*100</f>
-        <v>4</v>
-      </c>
-      <c r="H22" s="2">
-        <v>5550</v>
-      </c>
-      <c r="I22" s="4">
-        <f t="shared" ref="I22" si="11">H22/100000*100</f>
-        <v>5.55</v>
-      </c>
+      <c r="A22" s="5"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="4"/>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="5"/>
@@ -1303,17 +1280,6 @@
       <c r="G37" s="3"/>
       <c r="H37" s="2"/>
       <c r="I37" s="4"/>
-    </row>
-    <row r="38" spans="1:9">
-      <c r="A38" s="5"/>
-      <c r="B38" s="2"/>
-      <c r="C38" s="3"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="3"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/assets/newportfoliodata.xlsx
+++ b/src/assets/newportfoliodata.xlsx
@@ -89,7 +89,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -108,6 +108,12 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -403,10 +409,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" customWidth="1"/>
+    <col min="1" max="1" width="14.85546875" style="8" customWidth="1"/>
     <col min="3" max="3" width="15.28515625" customWidth="1"/>
     <col min="4" max="4" width="11.42578125" customWidth="1"/>
     <col min="5" max="5" width="17.28515625" customWidth="1"/>
@@ -1106,7 +1112,7 @@
       </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="5"/>
+      <c r="A22" s="6"/>
       <c r="B22" s="2"/>
       <c r="C22" s="3"/>
       <c r="D22" s="2"/>
@@ -1128,158 +1134,1496 @@
       <c r="I23" s="4"/>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="5"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="4"/>
+      <c r="A24" s="5">
+        <v>45931</v>
+      </c>
+      <c r="B24" s="2">
+        <v>4000</v>
+      </c>
+      <c r="C24" s="3">
+        <f t="shared" ref="C24:C41" si="8">B24/100000*100</f>
+        <v>4</v>
+      </c>
+      <c r="D24" s="2">
+        <v>-3000</v>
+      </c>
+      <c r="E24" s="3">
+        <f t="shared" ref="E24:E41" si="9">D24/100000*100</f>
+        <v>-3</v>
+      </c>
+      <c r="F24" s="2">
+        <v>5000</v>
+      </c>
+      <c r="G24" s="3">
+        <f t="shared" ref="G24:G41" si="10">F24/100000*100</f>
+        <v>5</v>
+      </c>
+      <c r="H24" s="2">
+        <v>2050</v>
+      </c>
+      <c r="I24" s="4">
+        <f t="shared" ref="I24:I41" si="11">H24/100000*100</f>
+        <v>2.0500000000000003</v>
+      </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="5"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="4"/>
+      <c r="A25" s="5">
+        <v>45932</v>
+      </c>
+      <c r="B25" s="2">
+        <v>-1500</v>
+      </c>
+      <c r="C25" s="3">
+        <f t="shared" si="8"/>
+        <v>-1.5</v>
+      </c>
+      <c r="D25" s="2">
+        <v>2000</v>
+      </c>
+      <c r="E25" s="3">
+        <f t="shared" si="9"/>
+        <v>2</v>
+      </c>
+      <c r="F25" s="2">
+        <v>3050</v>
+      </c>
+      <c r="G25" s="3">
+        <f t="shared" si="10"/>
+        <v>3.05</v>
+      </c>
+      <c r="H25" s="2">
+        <v>6000</v>
+      </c>
+      <c r="I25" s="4">
+        <f t="shared" si="11"/>
+        <v>6</v>
+      </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="5"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="4"/>
+      <c r="A26" s="5">
+        <v>45933</v>
+      </c>
+      <c r="B26" s="2">
+        <v>3500</v>
+      </c>
+      <c r="C26" s="3">
+        <f t="shared" si="8"/>
+        <v>3.5000000000000004</v>
+      </c>
+      <c r="D26" s="2">
+        <v>3000</v>
+      </c>
+      <c r="E26" s="3">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="F26" s="2">
+        <v>-2000</v>
+      </c>
+      <c r="G26" s="3">
+        <f t="shared" si="10"/>
+        <v>-2</v>
+      </c>
+      <c r="H26" s="2">
+        <v>4000</v>
+      </c>
+      <c r="I26" s="4">
+        <f t="shared" si="11"/>
+        <v>4</v>
+      </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="5"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="4"/>
+      <c r="A27" s="5">
+        <v>45936</v>
+      </c>
+      <c r="B27" s="2">
+        <v>3800</v>
+      </c>
+      <c r="C27" s="3">
+        <f t="shared" si="8"/>
+        <v>3.8</v>
+      </c>
+      <c r="D27" s="2">
+        <v>4550</v>
+      </c>
+      <c r="E27" s="3">
+        <f t="shared" si="9"/>
+        <v>4.55</v>
+      </c>
+      <c r="F27" s="2">
+        <v>3000</v>
+      </c>
+      <c r="G27" s="3">
+        <f t="shared" si="10"/>
+        <v>3</v>
+      </c>
+      <c r="H27" s="2">
+        <v>-3000</v>
+      </c>
+      <c r="I27" s="4">
+        <f t="shared" si="11"/>
+        <v>-3</v>
+      </c>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="5"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="4"/>
+      <c r="A28" s="5">
+        <v>45937</v>
+      </c>
+      <c r="B28" s="2">
+        <v>4000</v>
+      </c>
+      <c r="C28" s="3">
+        <f t="shared" si="8"/>
+        <v>4</v>
+      </c>
+      <c r="D28" s="2">
+        <v>-3000</v>
+      </c>
+      <c r="E28" s="3">
+        <f t="shared" si="9"/>
+        <v>-3</v>
+      </c>
+      <c r="F28" s="2">
+        <v>5000</v>
+      </c>
+      <c r="G28" s="3">
+        <f t="shared" si="10"/>
+        <v>5</v>
+      </c>
+      <c r="H28" s="2">
+        <v>2050</v>
+      </c>
+      <c r="I28" s="4">
+        <f t="shared" si="11"/>
+        <v>2.0500000000000003</v>
+      </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="5"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="4"/>
+      <c r="A29" s="5">
+        <v>45938</v>
+      </c>
+      <c r="B29" s="2">
+        <v>-1500</v>
+      </c>
+      <c r="C29" s="3">
+        <f t="shared" si="8"/>
+        <v>-1.5</v>
+      </c>
+      <c r="D29" s="2">
+        <v>2000</v>
+      </c>
+      <c r="E29" s="3">
+        <f t="shared" si="9"/>
+        <v>2</v>
+      </c>
+      <c r="F29" s="2">
+        <v>3050</v>
+      </c>
+      <c r="G29" s="3">
+        <f t="shared" si="10"/>
+        <v>3.05</v>
+      </c>
+      <c r="H29" s="2">
+        <v>6000</v>
+      </c>
+      <c r="I29" s="4">
+        <f t="shared" si="11"/>
+        <v>6</v>
+      </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="5"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="4"/>
+      <c r="A30" s="5">
+        <v>45939</v>
+      </c>
+      <c r="B30" s="2">
+        <v>2500</v>
+      </c>
+      <c r="C30" s="3">
+        <f t="shared" si="8"/>
+        <v>2.5</v>
+      </c>
+      <c r="D30" s="2">
+        <v>3000</v>
+      </c>
+      <c r="E30" s="3">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="F30" s="2">
+        <v>2000</v>
+      </c>
+      <c r="G30" s="3">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="H30" s="2">
+        <v>3550</v>
+      </c>
+      <c r="I30" s="4">
+        <f t="shared" si="11"/>
+        <v>3.55</v>
+      </c>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="5"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="4"/>
+      <c r="A31" s="5">
+        <v>45940</v>
+      </c>
+      <c r="B31" s="2">
+        <v>3500</v>
+      </c>
+      <c r="C31" s="3">
+        <f t="shared" si="8"/>
+        <v>3.5000000000000004</v>
+      </c>
+      <c r="D31" s="2">
+        <v>3000</v>
+      </c>
+      <c r="E31" s="3">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="F31" s="2">
+        <v>-2000</v>
+      </c>
+      <c r="G31" s="3">
+        <f t="shared" si="10"/>
+        <v>-2</v>
+      </c>
+      <c r="H31" s="2">
+        <v>4000</v>
+      </c>
+      <c r="I31" s="4">
+        <f t="shared" si="11"/>
+        <v>4</v>
+      </c>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="5"/>
-      <c r="B32" s="2"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="4"/>
+      <c r="A32" s="5">
+        <v>45943</v>
+      </c>
+      <c r="B32" s="2">
+        <v>3800</v>
+      </c>
+      <c r="C32" s="3">
+        <f t="shared" si="8"/>
+        <v>3.8</v>
+      </c>
+      <c r="D32" s="2">
+        <v>4550</v>
+      </c>
+      <c r="E32" s="3">
+        <f t="shared" si="9"/>
+        <v>4.55</v>
+      </c>
+      <c r="F32" s="2">
+        <v>3000</v>
+      </c>
+      <c r="G32" s="3">
+        <f t="shared" si="10"/>
+        <v>3</v>
+      </c>
+      <c r="H32" s="2">
+        <v>-3000</v>
+      </c>
+      <c r="I32" s="4">
+        <f t="shared" si="11"/>
+        <v>-3</v>
+      </c>
     </row>
     <row r="33" spans="1:9">
-      <c r="A33" s="5"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="4"/>
+      <c r="A33" s="5">
+        <v>45944</v>
+      </c>
+      <c r="B33" s="2">
+        <v>4000</v>
+      </c>
+      <c r="C33" s="3">
+        <f t="shared" si="8"/>
+        <v>4</v>
+      </c>
+      <c r="D33" s="2">
+        <v>-3000</v>
+      </c>
+      <c r="E33" s="3">
+        <f t="shared" si="9"/>
+        <v>-3</v>
+      </c>
+      <c r="F33" s="2">
+        <v>5000</v>
+      </c>
+      <c r="G33" s="3">
+        <f t="shared" si="10"/>
+        <v>5</v>
+      </c>
+      <c r="H33" s="2">
+        <v>2050</v>
+      </c>
+      <c r="I33" s="4">
+        <f t="shared" si="11"/>
+        <v>2.0500000000000003</v>
+      </c>
     </row>
     <row r="34" spans="1:9">
-      <c r="A34" s="5"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="3"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="3"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="4"/>
+      <c r="A34" s="5">
+        <v>45945</v>
+      </c>
+      <c r="B34" s="2">
+        <v>-1500</v>
+      </c>
+      <c r="C34" s="3">
+        <f t="shared" si="8"/>
+        <v>-1.5</v>
+      </c>
+      <c r="D34" s="2">
+        <v>2000</v>
+      </c>
+      <c r="E34" s="3">
+        <f t="shared" si="9"/>
+        <v>2</v>
+      </c>
+      <c r="F34" s="2">
+        <v>3050</v>
+      </c>
+      <c r="G34" s="3">
+        <f t="shared" si="10"/>
+        <v>3.05</v>
+      </c>
+      <c r="H34" s="2">
+        <v>6000</v>
+      </c>
+      <c r="I34" s="4">
+        <f t="shared" si="11"/>
+        <v>6</v>
+      </c>
     </row>
     <row r="35" spans="1:9">
-      <c r="A35" s="5"/>
-      <c r="B35" s="2"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="3"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="3"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="4"/>
+      <c r="A35" s="5">
+        <v>45946</v>
+      </c>
+      <c r="B35" s="2">
+        <v>-1500</v>
+      </c>
+      <c r="C35" s="3">
+        <f t="shared" si="8"/>
+        <v>-1.5</v>
+      </c>
+      <c r="D35" s="2">
+        <v>2000</v>
+      </c>
+      <c r="E35" s="3">
+        <f t="shared" si="9"/>
+        <v>2</v>
+      </c>
+      <c r="F35" s="2">
+        <v>3050</v>
+      </c>
+      <c r="G35" s="3">
+        <f t="shared" si="10"/>
+        <v>3.05</v>
+      </c>
+      <c r="H35" s="2">
+        <v>6000</v>
+      </c>
+      <c r="I35" s="4">
+        <f t="shared" si="11"/>
+        <v>6</v>
+      </c>
     </row>
     <row r="36" spans="1:9">
-      <c r="A36" s="5"/>
-      <c r="B36" s="2"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="3"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="4"/>
+      <c r="A36" s="5">
+        <v>45947</v>
+      </c>
+      <c r="B36" s="2">
+        <v>2500</v>
+      </c>
+      <c r="C36" s="3">
+        <f t="shared" si="8"/>
+        <v>2.5</v>
+      </c>
+      <c r="D36" s="2">
+        <v>3000</v>
+      </c>
+      <c r="E36" s="3">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="F36" s="2">
+        <v>2000</v>
+      </c>
+      <c r="G36" s="3">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="H36" s="2">
+        <v>3550</v>
+      </c>
+      <c r="I36" s="4">
+        <f t="shared" si="11"/>
+        <v>3.55</v>
+      </c>
     </row>
     <row r="37" spans="1:9">
-      <c r="A37" s="5"/>
-      <c r="B37" s="2"/>
-      <c r="C37" s="3"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="3"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="3"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="4"/>
+      <c r="A37" s="5">
+        <v>45950</v>
+      </c>
+      <c r="B37" s="2">
+        <v>3800</v>
+      </c>
+      <c r="C37" s="3">
+        <f t="shared" si="8"/>
+        <v>3.8</v>
+      </c>
+      <c r="D37" s="2">
+        <v>4550</v>
+      </c>
+      <c r="E37" s="3">
+        <f t="shared" si="9"/>
+        <v>4.55</v>
+      </c>
+      <c r="F37" s="2">
+        <v>3000</v>
+      </c>
+      <c r="G37" s="3">
+        <f t="shared" si="10"/>
+        <v>3</v>
+      </c>
+      <c r="H37" s="2">
+        <v>-3000</v>
+      </c>
+      <c r="I37" s="4">
+        <f t="shared" si="11"/>
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" s="7">
+        <v>45951</v>
+      </c>
+      <c r="B38" s="2">
+        <v>4000</v>
+      </c>
+      <c r="C38" s="3">
+        <f t="shared" si="8"/>
+        <v>4</v>
+      </c>
+      <c r="D38" s="2">
+        <v>-3000</v>
+      </c>
+      <c r="E38" s="3">
+        <f t="shared" si="9"/>
+        <v>-3</v>
+      </c>
+      <c r="F38" s="2">
+        <v>5000</v>
+      </c>
+      <c r="G38" s="3">
+        <f t="shared" si="10"/>
+        <v>5</v>
+      </c>
+      <c r="H38" s="2">
+        <v>2050</v>
+      </c>
+      <c r="I38" s="4">
+        <f t="shared" si="11"/>
+        <v>2.0500000000000003</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" s="7">
+        <v>45952</v>
+      </c>
+      <c r="B39" s="2">
+        <v>-1500</v>
+      </c>
+      <c r="C39" s="3">
+        <f t="shared" si="8"/>
+        <v>-1.5</v>
+      </c>
+      <c r="D39" s="2">
+        <v>2000</v>
+      </c>
+      <c r="E39" s="3">
+        <f t="shared" si="9"/>
+        <v>2</v>
+      </c>
+      <c r="F39" s="2">
+        <v>3050</v>
+      </c>
+      <c r="G39" s="3">
+        <f t="shared" si="10"/>
+        <v>3.05</v>
+      </c>
+      <c r="H39" s="2">
+        <v>6000</v>
+      </c>
+      <c r="I39" s="4">
+        <f t="shared" si="11"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" s="7">
+        <v>45953</v>
+      </c>
+      <c r="B40" s="2">
+        <v>2500</v>
+      </c>
+      <c r="C40" s="3">
+        <f t="shared" si="8"/>
+        <v>2.5</v>
+      </c>
+      <c r="D40" s="2">
+        <v>3000</v>
+      </c>
+      <c r="E40" s="3">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="F40" s="2">
+        <v>2000</v>
+      </c>
+      <c r="G40" s="3">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="H40" s="2">
+        <v>3550</v>
+      </c>
+      <c r="I40" s="4">
+        <f t="shared" si="11"/>
+        <v>3.55</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" s="7">
+        <v>45954</v>
+      </c>
+      <c r="B41" s="2">
+        <v>3500</v>
+      </c>
+      <c r="C41" s="3">
+        <f t="shared" si="8"/>
+        <v>3.5000000000000004</v>
+      </c>
+      <c r="D41" s="2">
+        <v>3000</v>
+      </c>
+      <c r="E41" s="3">
+        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="F41" s="2">
+        <v>4000</v>
+      </c>
+      <c r="G41" s="3">
+        <f t="shared" si="10"/>
+        <v>4</v>
+      </c>
+      <c r="H41" s="2">
+        <v>5550</v>
+      </c>
+      <c r="I41" s="4">
+        <f t="shared" si="11"/>
+        <v>5.55</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" s="7">
+        <v>45957</v>
+      </c>
+      <c r="B42" s="2">
+        <v>3500</v>
+      </c>
+      <c r="C42" s="3">
+        <f>B42/100000*100</f>
+        <v>3.5000000000000004</v>
+      </c>
+      <c r="D42" s="2">
+        <v>3000</v>
+      </c>
+      <c r="E42" s="3">
+        <f>D42/100000*100</f>
+        <v>3</v>
+      </c>
+      <c r="F42" s="2">
+        <v>-2000</v>
+      </c>
+      <c r="G42" s="3">
+        <f>F42/100000*100</f>
+        <v>-2</v>
+      </c>
+      <c r="H42" s="2">
+        <v>4000</v>
+      </c>
+      <c r="I42" s="4">
+        <f>H42/100000*100</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" s="7">
+        <v>45958</v>
+      </c>
+      <c r="B43" s="2">
+        <v>3800</v>
+      </c>
+      <c r="C43" s="3">
+        <f t="shared" ref="C43:C60" si="12">B43/100000*100</f>
+        <v>3.8</v>
+      </c>
+      <c r="D43" s="2">
+        <v>4550</v>
+      </c>
+      <c r="E43" s="3">
+        <f t="shared" ref="E43:E60" si="13">D43/100000*100</f>
+        <v>4.55</v>
+      </c>
+      <c r="F43" s="2">
+        <v>3000</v>
+      </c>
+      <c r="G43" s="3">
+        <f t="shared" ref="G43:G60" si="14">F43/100000*100</f>
+        <v>3</v>
+      </c>
+      <c r="H43" s="2">
+        <v>-3000</v>
+      </c>
+      <c r="I43" s="4">
+        <f t="shared" ref="I43:I60" si="15">H43/100000*100</f>
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" s="7"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="3"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="4"/>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" s="7"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="3"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="4"/>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" s="7">
+        <v>45964</v>
+      </c>
+      <c r="B46" s="2">
+        <v>3800</v>
+      </c>
+      <c r="C46" s="3">
+        <f t="shared" si="12"/>
+        <v>3.8</v>
+      </c>
+      <c r="D46" s="2">
+        <v>4550</v>
+      </c>
+      <c r="E46" s="3">
+        <f t="shared" si="13"/>
+        <v>4.55</v>
+      </c>
+      <c r="F46" s="2">
+        <v>3000</v>
+      </c>
+      <c r="G46" s="3">
+        <f t="shared" si="14"/>
+        <v>3</v>
+      </c>
+      <c r="H46" s="2">
+        <v>-3000</v>
+      </c>
+      <c r="I46" s="4">
+        <f t="shared" si="15"/>
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" s="7">
+        <v>45965</v>
+      </c>
+      <c r="B47" s="2">
+        <v>4000</v>
+      </c>
+      <c r="C47" s="3">
+        <f t="shared" si="12"/>
+        <v>4</v>
+      </c>
+      <c r="D47" s="2">
+        <v>-3000</v>
+      </c>
+      <c r="E47" s="3">
+        <f t="shared" si="13"/>
+        <v>-3</v>
+      </c>
+      <c r="F47" s="2">
+        <v>5000</v>
+      </c>
+      <c r="G47" s="3">
+        <f t="shared" si="14"/>
+        <v>5</v>
+      </c>
+      <c r="H47" s="2">
+        <v>2050</v>
+      </c>
+      <c r="I47" s="4">
+        <f t="shared" si="15"/>
+        <v>2.0500000000000003</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" s="7">
+        <v>45966</v>
+      </c>
+      <c r="B48" s="2">
+        <v>-1500</v>
+      </c>
+      <c r="C48" s="3">
+        <f t="shared" si="12"/>
+        <v>-1.5</v>
+      </c>
+      <c r="D48" s="2">
+        <v>2000</v>
+      </c>
+      <c r="E48" s="3">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
+      <c r="F48" s="2">
+        <v>3050</v>
+      </c>
+      <c r="G48" s="3">
+        <f t="shared" si="14"/>
+        <v>3.05</v>
+      </c>
+      <c r="H48" s="2">
+        <v>6000</v>
+      </c>
+      <c r="I48" s="4">
+        <f t="shared" si="15"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49" s="7">
+        <v>45967</v>
+      </c>
+      <c r="B49" s="2">
+        <v>2500</v>
+      </c>
+      <c r="C49" s="3">
+        <f t="shared" si="12"/>
+        <v>2.5</v>
+      </c>
+      <c r="D49" s="2">
+        <v>3000</v>
+      </c>
+      <c r="E49" s="3">
+        <f t="shared" si="13"/>
+        <v>3</v>
+      </c>
+      <c r="F49" s="2">
+        <v>2000</v>
+      </c>
+      <c r="G49" s="3">
+        <f t="shared" si="14"/>
+        <v>2</v>
+      </c>
+      <c r="H49" s="2">
+        <v>3550</v>
+      </c>
+      <c r="I49" s="4">
+        <f t="shared" si="15"/>
+        <v>3.55</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="A50" s="7">
+        <v>45968</v>
+      </c>
+      <c r="B50" s="2">
+        <v>3500</v>
+      </c>
+      <c r="C50" s="3">
+        <f t="shared" si="12"/>
+        <v>3.5000000000000004</v>
+      </c>
+      <c r="D50" s="2">
+        <v>3000</v>
+      </c>
+      <c r="E50" s="3">
+        <f t="shared" si="13"/>
+        <v>3</v>
+      </c>
+      <c r="F50" s="2">
+        <v>-2000</v>
+      </c>
+      <c r="G50" s="3">
+        <f t="shared" si="14"/>
+        <v>-2</v>
+      </c>
+      <c r="H50" s="2">
+        <v>4000</v>
+      </c>
+      <c r="I50" s="4">
+        <f t="shared" si="15"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51" s="7">
+        <v>45971</v>
+      </c>
+      <c r="B51" s="2">
+        <v>3800</v>
+      </c>
+      <c r="C51" s="3">
+        <f t="shared" si="12"/>
+        <v>3.8</v>
+      </c>
+      <c r="D51" s="2">
+        <v>4550</v>
+      </c>
+      <c r="E51" s="3">
+        <f t="shared" si="13"/>
+        <v>4.55</v>
+      </c>
+      <c r="F51" s="2">
+        <v>3000</v>
+      </c>
+      <c r="G51" s="3">
+        <f t="shared" si="14"/>
+        <v>3</v>
+      </c>
+      <c r="H51" s="2">
+        <v>-3000</v>
+      </c>
+      <c r="I51" s="4">
+        <f t="shared" si="15"/>
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
+      <c r="A52" s="7">
+        <v>45972</v>
+      </c>
+      <c r="B52" s="2">
+        <v>4000</v>
+      </c>
+      <c r="C52" s="3">
+        <f t="shared" si="12"/>
+        <v>4</v>
+      </c>
+      <c r="D52" s="2">
+        <v>-3000</v>
+      </c>
+      <c r="E52" s="3">
+        <f t="shared" si="13"/>
+        <v>-3</v>
+      </c>
+      <c r="F52" s="2">
+        <v>5000</v>
+      </c>
+      <c r="G52" s="3">
+        <f t="shared" si="14"/>
+        <v>5</v>
+      </c>
+      <c r="H52" s="2">
+        <v>2050</v>
+      </c>
+      <c r="I52" s="4">
+        <f t="shared" si="15"/>
+        <v>2.0500000000000003</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="A53" s="7">
+        <v>45973</v>
+      </c>
+      <c r="B53" s="2">
+        <v>-1500</v>
+      </c>
+      <c r="C53" s="3">
+        <f t="shared" si="12"/>
+        <v>-1.5</v>
+      </c>
+      <c r="D53" s="2">
+        <v>2000</v>
+      </c>
+      <c r="E53" s="3">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
+      <c r="F53" s="2">
+        <v>3050</v>
+      </c>
+      <c r="G53" s="3">
+        <f t="shared" si="14"/>
+        <v>3.05</v>
+      </c>
+      <c r="H53" s="2">
+        <v>6000</v>
+      </c>
+      <c r="I53" s="4">
+        <f t="shared" si="15"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="A54" s="7">
+        <v>45974</v>
+      </c>
+      <c r="B54" s="2">
+        <v>-1500</v>
+      </c>
+      <c r="C54" s="3">
+        <f t="shared" si="12"/>
+        <v>-1.5</v>
+      </c>
+      <c r="D54" s="2">
+        <v>2000</v>
+      </c>
+      <c r="E54" s="3">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
+      <c r="F54" s="2">
+        <v>3050</v>
+      </c>
+      <c r="G54" s="3">
+        <f t="shared" si="14"/>
+        <v>3.05</v>
+      </c>
+      <c r="H54" s="2">
+        <v>6000</v>
+      </c>
+      <c r="I54" s="4">
+        <f t="shared" si="15"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
+      <c r="A55" s="7">
+        <v>45975</v>
+      </c>
+      <c r="B55" s="2">
+        <v>2500</v>
+      </c>
+      <c r="C55" s="3">
+        <f t="shared" si="12"/>
+        <v>2.5</v>
+      </c>
+      <c r="D55" s="2">
+        <v>3000</v>
+      </c>
+      <c r="E55" s="3">
+        <f t="shared" si="13"/>
+        <v>3</v>
+      </c>
+      <c r="F55" s="2">
+        <v>2000</v>
+      </c>
+      <c r="G55" s="3">
+        <f t="shared" si="14"/>
+        <v>2</v>
+      </c>
+      <c r="H55" s="2">
+        <v>3550</v>
+      </c>
+      <c r="I55" s="4">
+        <f t="shared" si="15"/>
+        <v>3.55</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
+      <c r="A56" s="7">
+        <v>45978</v>
+      </c>
+      <c r="B56" s="2">
+        <v>3800</v>
+      </c>
+      <c r="C56" s="3">
+        <f t="shared" si="12"/>
+        <v>3.8</v>
+      </c>
+      <c r="D56" s="2">
+        <v>4550</v>
+      </c>
+      <c r="E56" s="3">
+        <f t="shared" si="13"/>
+        <v>4.55</v>
+      </c>
+      <c r="F56" s="2">
+        <v>3000</v>
+      </c>
+      <c r="G56" s="3">
+        <f t="shared" si="14"/>
+        <v>3</v>
+      </c>
+      <c r="H56" s="2">
+        <v>-3000</v>
+      </c>
+      <c r="I56" s="4">
+        <f t="shared" si="15"/>
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
+      <c r="A57" s="7">
+        <v>45979</v>
+      </c>
+      <c r="B57" s="2">
+        <v>4000</v>
+      </c>
+      <c r="C57" s="3">
+        <f t="shared" si="12"/>
+        <v>4</v>
+      </c>
+      <c r="D57" s="2">
+        <v>-3000</v>
+      </c>
+      <c r="E57" s="3">
+        <f t="shared" si="13"/>
+        <v>-3</v>
+      </c>
+      <c r="F57" s="2">
+        <v>5000</v>
+      </c>
+      <c r="G57" s="3">
+        <f t="shared" si="14"/>
+        <v>5</v>
+      </c>
+      <c r="H57" s="2">
+        <v>2050</v>
+      </c>
+      <c r="I57" s="4">
+        <f t="shared" si="15"/>
+        <v>2.0500000000000003</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
+      <c r="A58" s="7">
+        <v>45980</v>
+      </c>
+      <c r="B58" s="2">
+        <v>-1500</v>
+      </c>
+      <c r="C58" s="3">
+        <f t="shared" si="12"/>
+        <v>-1.5</v>
+      </c>
+      <c r="D58" s="2">
+        <v>2000</v>
+      </c>
+      <c r="E58" s="3">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
+      <c r="F58" s="2">
+        <v>3050</v>
+      </c>
+      <c r="G58" s="3">
+        <f t="shared" si="14"/>
+        <v>3.05</v>
+      </c>
+      <c r="H58" s="2">
+        <v>6000</v>
+      </c>
+      <c r="I58" s="4">
+        <f t="shared" si="15"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
+      <c r="A59" s="7">
+        <v>45981</v>
+      </c>
+      <c r="B59" s="2">
+        <v>2500</v>
+      </c>
+      <c r="C59" s="3">
+        <f t="shared" si="12"/>
+        <v>2.5</v>
+      </c>
+      <c r="D59" s="2">
+        <v>3000</v>
+      </c>
+      <c r="E59" s="3">
+        <f t="shared" si="13"/>
+        <v>3</v>
+      </c>
+      <c r="F59" s="2">
+        <v>2000</v>
+      </c>
+      <c r="G59" s="3">
+        <f t="shared" si="14"/>
+        <v>2</v>
+      </c>
+      <c r="H59" s="2">
+        <v>3550</v>
+      </c>
+      <c r="I59" s="4">
+        <f t="shared" si="15"/>
+        <v>3.55</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
+      <c r="A60" s="7">
+        <v>45982</v>
+      </c>
+      <c r="B60" s="2">
+        <v>3500</v>
+      </c>
+      <c r="C60" s="3">
+        <f t="shared" si="12"/>
+        <v>3.5000000000000004</v>
+      </c>
+      <c r="D60" s="2">
+        <v>3000</v>
+      </c>
+      <c r="E60" s="3">
+        <f t="shared" si="13"/>
+        <v>3</v>
+      </c>
+      <c r="F60" s="2">
+        <v>4000</v>
+      </c>
+      <c r="G60" s="3">
+        <f t="shared" si="14"/>
+        <v>4</v>
+      </c>
+      <c r="H60" s="2">
+        <v>5550</v>
+      </c>
+      <c r="I60" s="4">
+        <f t="shared" si="15"/>
+        <v>5.55</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
+      <c r="A61" s="7">
+        <v>45985</v>
+      </c>
+      <c r="B61" s="2">
+        <v>3500</v>
+      </c>
+      <c r="C61" s="3">
+        <f>B61/100000*100</f>
+        <v>3.5000000000000004</v>
+      </c>
+      <c r="D61" s="2">
+        <v>3000</v>
+      </c>
+      <c r="E61" s="3">
+        <f>D61/100000*100</f>
+        <v>3</v>
+      </c>
+      <c r="F61" s="2">
+        <v>-2000</v>
+      </c>
+      <c r="G61" s="3">
+        <f>F61/100000*100</f>
+        <v>-2</v>
+      </c>
+      <c r="H61" s="2">
+        <v>4000</v>
+      </c>
+      <c r="I61" s="4">
+        <f>H61/100000*100</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9">
+      <c r="A62" s="7">
+        <v>45986</v>
+      </c>
+      <c r="B62" s="2">
+        <v>3800</v>
+      </c>
+      <c r="C62" s="3">
+        <f t="shared" ref="C62:C65" si="16">B62/100000*100</f>
+        <v>3.8</v>
+      </c>
+      <c r="D62" s="2">
+        <v>4550</v>
+      </c>
+      <c r="E62" s="3">
+        <f t="shared" ref="E62:E65" si="17">D62/100000*100</f>
+        <v>4.55</v>
+      </c>
+      <c r="F62" s="2">
+        <v>3000</v>
+      </c>
+      <c r="G62" s="3">
+        <f t="shared" ref="G62:G65" si="18">F62/100000*100</f>
+        <v>3</v>
+      </c>
+      <c r="H62" s="2">
+        <v>-3000</v>
+      </c>
+      <c r="I62" s="4">
+        <f t="shared" ref="I62:I65" si="19">H62/100000*100</f>
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
+      <c r="A63" s="7">
+        <v>45987</v>
+      </c>
+      <c r="B63" s="2">
+        <v>4000</v>
+      </c>
+      <c r="C63" s="3">
+        <f t="shared" si="16"/>
+        <v>4</v>
+      </c>
+      <c r="D63" s="2">
+        <v>-3000</v>
+      </c>
+      <c r="E63" s="3">
+        <f t="shared" si="17"/>
+        <v>-3</v>
+      </c>
+      <c r="F63" s="2">
+        <v>5000</v>
+      </c>
+      <c r="G63" s="3">
+        <f t="shared" si="18"/>
+        <v>5</v>
+      </c>
+      <c r="H63" s="2">
+        <v>2050</v>
+      </c>
+      <c r="I63" s="4">
+        <f t="shared" si="19"/>
+        <v>2.0500000000000003</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
+      <c r="A64" s="7">
+        <v>45988</v>
+      </c>
+      <c r="B64" s="2">
+        <v>-1500</v>
+      </c>
+      <c r="C64" s="3">
+        <f t="shared" si="16"/>
+        <v>-1.5</v>
+      </c>
+      <c r="D64" s="2">
+        <v>2000</v>
+      </c>
+      <c r="E64" s="3">
+        <f t="shared" si="17"/>
+        <v>2</v>
+      </c>
+      <c r="F64" s="2">
+        <v>3050</v>
+      </c>
+      <c r="G64" s="3">
+        <f t="shared" si="18"/>
+        <v>3.05</v>
+      </c>
+      <c r="H64" s="2">
+        <v>6000</v>
+      </c>
+      <c r="I64" s="4">
+        <f t="shared" si="19"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9">
+      <c r="A65" s="7">
+        <v>45989</v>
+      </c>
+      <c r="B65" s="2">
+        <v>3500</v>
+      </c>
+      <c r="C65" s="3">
+        <f t="shared" si="16"/>
+        <v>3.5000000000000004</v>
+      </c>
+      <c r="D65" s="2">
+        <v>3000</v>
+      </c>
+      <c r="E65" s="3">
+        <f t="shared" si="17"/>
+        <v>3</v>
+      </c>
+      <c r="F65" s="2">
+        <v>-2000</v>
+      </c>
+      <c r="G65" s="3">
+        <f t="shared" si="18"/>
+        <v>-2</v>
+      </c>
+      <c r="H65" s="2">
+        <v>4000</v>
+      </c>
+      <c r="I65" s="4">
+        <f t="shared" si="19"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9">
+      <c r="B66" s="2"/>
+      <c r="C66" s="3"/>
+      <c r="D66" s="2"/>
+      <c r="E66" s="3"/>
+      <c r="F66" s="2"/>
+      <c r="G66" s="3"/>
+      <c r="H66" s="2"/>
+      <c r="I66" s="4"/>
+    </row>
+    <row r="67" spans="1:9">
+      <c r="B67" s="2"/>
+      <c r="C67" s="3"/>
+      <c r="D67" s="2"/>
+      <c r="E67" s="3"/>
+      <c r="F67" s="2"/>
+      <c r="G67" s="3"/>
+      <c r="H67" s="2"/>
+      <c r="I67" s="4"/>
+    </row>
+    <row r="68" spans="1:9">
+      <c r="B68" s="2"/>
+      <c r="C68" s="3"/>
+      <c r="D68" s="2"/>
+      <c r="E68" s="3"/>
+      <c r="F68" s="2"/>
+      <c r="G68" s="3"/>
+      <c r="H68" s="2"/>
+      <c r="I68" s="4"/>
+    </row>
+    <row r="69" spans="1:9">
+      <c r="B69" s="2"/>
+      <c r="C69" s="3"/>
+      <c r="D69" s="2"/>
+      <c r="E69" s="3"/>
+      <c r="F69" s="2"/>
+      <c r="G69" s="3"/>
+      <c r="H69" s="2"/>
+      <c r="I69" s="4"/>
+    </row>
+    <row r="70" spans="1:9">
+      <c r="B70" s="2"/>
+      <c r="C70" s="3"/>
+      <c r="D70" s="2"/>
+      <c r="E70" s="3"/>
+      <c r="F70" s="2"/>
+      <c r="G70" s="3"/>
+      <c r="H70" s="2"/>
+      <c r="I70" s="4"/>
+    </row>
+    <row r="71" spans="1:9">
+      <c r="B71" s="2"/>
+      <c r="C71" s="3"/>
+      <c r="D71" s="2"/>
+      <c r="E71" s="3"/>
+      <c r="F71" s="2"/>
+      <c r="G71" s="3"/>
+      <c r="H71" s="2"/>
+      <c r="I71" s="4"/>
+    </row>
+    <row r="72" spans="1:9">
+      <c r="B72" s="2"/>
+      <c r="C72" s="3"/>
+      <c r="D72" s="2"/>
+      <c r="E72" s="3"/>
+      <c r="F72" s="2"/>
+      <c r="G72" s="3"/>
+      <c r="H72" s="2"/>
+      <c r="I72" s="4"/>
+    </row>
+    <row r="73" spans="1:9">
+      <c r="B73" s="2"/>
+      <c r="C73" s="3"/>
+      <c r="D73" s="2"/>
+      <c r="E73" s="3"/>
+      <c r="F73" s="2"/>
+      <c r="G73" s="3"/>
+      <c r="H73" s="2"/>
+      <c r="I73" s="4"/>
+    </row>
+    <row r="74" spans="1:9">
+      <c r="B74" s="2"/>
+      <c r="C74" s="3"/>
+      <c r="D74" s="2"/>
+      <c r="E74" s="3"/>
+      <c r="F74" s="2"/>
+      <c r="G74" s="3"/>
+      <c r="H74" s="2"/>
+      <c r="I74" s="4"/>
+    </row>
+    <row r="75" spans="1:9">
+      <c r="B75" s="2"/>
+      <c r="C75" s="3"/>
+      <c r="D75" s="2"/>
+      <c r="E75" s="3"/>
+      <c r="F75" s="2"/>
+      <c r="G75" s="3"/>
+      <c r="H75" s="2"/>
+      <c r="I75" s="4"/>
+    </row>
+    <row r="76" spans="1:9">
+      <c r="B76" s="2"/>
+      <c r="C76" s="3"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="3"/>
+      <c r="F76" s="2"/>
+      <c r="G76" s="3"/>
+      <c r="H76" s="2"/>
+      <c r="I76" s="4"/>
+    </row>
+    <row r="77" spans="1:9">
+      <c r="B77" s="2"/>
+      <c r="C77" s="3"/>
+      <c r="D77" s="2"/>
+      <c r="E77" s="3"/>
+      <c r="F77" s="2"/>
+      <c r="G77" s="3"/>
+      <c r="H77" s="2"/>
+      <c r="I77" s="4"/>
+    </row>
+    <row r="78" spans="1:9">
+      <c r="B78" s="2"/>
+      <c r="C78" s="3"/>
+      <c r="D78" s="2"/>
+      <c r="E78" s="3"/>
+      <c r="F78" s="2"/>
+      <c r="G78" s="3"/>
+      <c r="H78" s="2"/>
+      <c r="I78" s="4"/>
+    </row>
+    <row r="79" spans="1:9">
+      <c r="B79" s="2"/>
+      <c r="C79" s="3"/>
+      <c r="D79" s="2"/>
+      <c r="E79" s="3"/>
+      <c r="F79" s="2"/>
+      <c r="G79" s="3"/>
+      <c r="H79" s="2"/>
+      <c r="I79" s="4"/>
+    </row>
+    <row r="80" spans="1:9">
+      <c r="B80" s="2"/>
+      <c r="C80" s="3"/>
+      <c r="D80" s="2"/>
+      <c r="E80" s="3"/>
+      <c r="F80" s="2"/>
+      <c r="G80" s="3"/>
+      <c r="H80" s="2"/>
+      <c r="I80" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
